--- a/artfynd/A 29698-2025 artfynd.xlsx
+++ b/artfynd/A 29698-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129577445</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129554645</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>129554474</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29698-2025 artfynd.xlsx
+++ b/artfynd/A 29698-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129577445</v>
       </c>
       <c r="B2" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129554645</v>
       </c>
       <c r="B3" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>129554474</v>
       </c>
       <c r="B4" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29698-2025 artfynd.xlsx
+++ b/artfynd/A 29698-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129577445</v>
       </c>
       <c r="B2" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129554645</v>
       </c>
       <c r="B3" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>129554474</v>
       </c>
       <c r="B4" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29698-2025 artfynd.xlsx
+++ b/artfynd/A 29698-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129577445</v>
       </c>
       <c r="B2" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129554645</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>129554474</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29698-2025 artfynd.xlsx
+++ b/artfynd/A 29698-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129577445</v>
       </c>
       <c r="B2" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129554645</v>
       </c>
       <c r="B3" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>129554474</v>
       </c>
       <c r="B4" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
